--- a/experiment_results/wu_calibration/rtt_bursts_rps1_att4_WU200000.xlsx
+++ b/experiment_results/wu_calibration/rtt_bursts_rps1_att4_WU200000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.0</t>
+          <t>00:020.1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:039.9</t>
+          <t>00:040.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.6</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.1</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,12 +818,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.5</t>
+          <t>01:010.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.7</t>
+          <t>01:019.8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.7</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.4</t>
+          <t>01:039.8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.8</t>
+          <t>01:049.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.0</t>
+          <t>02:000.3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.3</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.5</t>
+          <t>02:020.1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,22 +1279,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.6</t>
+          <t>02:049.7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.2</t>
+          <t>02:054.8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,63 +1494,6 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
